--- a/upload/internacoes-via-urgencia.xlsx
+++ b/upload/internacoes-via-urgencia.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R476a3221c0cb4adc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R309a42bc2c55492c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2633,6 +2633,25 @@
     <x:row>
       <x:c t="inlineStr">
         <x:is>
+          <x:t>CSSI</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2747</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
           <x:t>HAC</x:t>
         </x:is>
       </x:c>
@@ -2760,7 +2779,7 @@
         <x:v>133</x:v>
       </x:c>
       <x:c s="8">
-        <x:v>317</x:v>
+        <x:v>318</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2785,6 +2804,25 @@
     <x:row>
       <x:c t="inlineStr">
         <x:is>
+          <x:t>HAC</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>323</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
           <x:t>HJK</x:t>
         </x:is>
       </x:c>
@@ -2817,7 +2855,7 @@
         <x:v>860</x:v>
       </x:c>
       <x:c s="8">
-        <x:v>5016</x:v>
+        <x:v>5017</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2836,7 +2874,7 @@
         <x:v>771</x:v>
       </x:c>
       <x:c s="8">
-        <x:v>5118</x:v>
+        <x:v>5119</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2852,10 +2890,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c s="8">
-        <x:v>792</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>5278</x:v>
+        <x:v>791</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>5280</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2871,10 +2909,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c s="8">
-        <x:v>868</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>5222</x:v>
+        <x:v>865</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>5225</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2890,10 +2928,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c s="8">
-        <x:v>834</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>5565</x:v>
+        <x:v>833</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>5566</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2918,6 +2956,25 @@
     <x:row>
       <x:c t="inlineStr">
         <x:is>
+          <x:t>HJK</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>5243</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
           <x:t>HRBJA</x:t>
         </x:is>
       </x:c>
@@ -3061,16 +3118,377 @@
         <x:v>8</x:v>
       </x:c>
       <x:c s="8">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2447</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1243</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>404</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>359</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>379</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>411</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>383</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>427</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>360</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>360</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>407</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>IRS</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>248</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>IRS</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>249</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>IRS</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>228</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>IRS</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>248</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>IRS</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>263</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>IRS</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>227</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>IRS</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>232</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>IRS</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c s="8">
         <x:v>243</x:v>
       </x:c>
-      <x:c s="8">
-        <x:v>2449</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>IRS</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -3080,54 +3498,54 @@
         <x:v>1</x:v>
       </x:c>
       <x:c s="8">
-        <x:v>157</x:v>
+        <x:v>359</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1461</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1278</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>3</x:v>
       </x:c>
       <x:c s="8">
         <x:v>404</x:v>
       </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>359</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>379</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
+      <x:c s="8">
+        <x:v>1473</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -3137,16 +3555,16 @@
         <x:v>4</x:v>
       </x:c>
       <x:c s="8">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>411</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
+        <x:v>380</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1380</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -3156,16 +3574,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c s="8">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>383</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
+        <x:v>381</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1265</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -3175,16 +3593,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c s="8">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>427</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
+        <x:v>355</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1230</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -3194,16 +3612,16 @@
         <x:v>7</x:v>
       </x:c>
       <x:c s="8">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>360</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
+        <x:v>349</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1467</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -3213,314 +3631,29 @@
         <x:v>8</x:v>
       </x:c>
       <x:c s="8">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>360</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>IRS</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>248</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>IRS</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>249</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>IRS</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>228</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>IRS</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>248</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>IRS</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>263</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>IRS</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>227</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>IRS</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>232</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>IRS</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>243</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>359</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1461</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>353</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1278</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>404</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1473</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>380</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1380</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>381</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1265</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>355</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1230</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>349</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1467</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c s="8">
         <x:v>363</x:v>
       </x:c>
       <x:c s="8">
         <x:v>1394</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1410</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3532,10 +3665,10 @@
       <x:c s="9"/>
       <x:c s="9"/>
       <x:c s="9">
-        <x:v>36109</x:v>
+        <x:v>37857</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>270626</x:v>
+        <x:v>282243</x:v>
       </x:c>
     </x:row>
     <x:row/>
